--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -356,6 +356,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>198</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -648,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -660,14 +685,23 @@
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -751,84 +785,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -837,462 +951,848 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
+        <v/>
+      </c>
+      <c r="T3" t="n">
+        <v/>
+      </c>
+      <c r="U3" t="n">
+        <v/>
+      </c>
+      <c r="V3" t="n">
+        <v/>
+      </c>
+      <c r="W3" t="n">
+        <v/>
+      </c>
+      <c r="X3" t="n">
+        <v/>
+      </c>
+      <c r="Y3" t="n">
+        <v/>
+      </c>
+      <c r="Z3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
+        <v/>
+      </c>
+      <c r="T4" t="n">
+        <v/>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
+      </c>
+      <c r="Z4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
+        <v/>
+      </c>
+      <c r="T5" t="n">
+        <v/>
+      </c>
+      <c r="U5" t="n">
+        <v/>
+      </c>
+      <c r="V5" t="n">
+        <v/>
+      </c>
+      <c r="W5" t="n">
+        <v/>
+      </c>
+      <c r="X5" t="n">
+        <v/>
+      </c>
+      <c r="Y5" t="n">
+        <v/>
+      </c>
+      <c r="Z5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
+        <v/>
+      </c>
+      <c r="T6" t="n">
+        <v/>
+      </c>
+      <c r="U6" t="n">
+        <v/>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
+      </c>
+      <c r="Z6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v/>
+      </c>
+      <c r="T10" t="n">
+        <v/>
+      </c>
+      <c r="U10" t="n">
+        <v/>
+      </c>
+      <c r="V10" t="n">
+        <v/>
+      </c>
+      <c r="W10" t="n">
+        <v/>
+      </c>
+      <c r="X10" t="n">
+        <v/>
+      </c>
+      <c r="Y10" t="n">
+        <v/>
+      </c>
+      <c r="Z10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -694,14 +694,23 @@
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -825,124 +834,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -951,848 +1040,1168 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v/>
-      </c>
-      <c r="T3" t="n">
-        <v/>
-      </c>
-      <c r="U3" t="n">
-        <v/>
-      </c>
-      <c r="V3" t="n">
-        <v/>
-      </c>
-      <c r="W3" t="n">
-        <v/>
-      </c>
-      <c r="X3" t="n">
-        <v/>
-      </c>
-      <c r="Y3" t="n">
-        <v/>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S4" t="n">
-        <v/>
-      </c>
-      <c r="T4" t="n">
-        <v/>
-      </c>
-      <c r="U4" t="n">
-        <v/>
-      </c>
-      <c r="V4" t="n">
-        <v/>
-      </c>
-      <c r="W4" t="n">
-        <v/>
-      </c>
-      <c r="X4" t="n">
-        <v/>
-      </c>
-      <c r="Y4" t="n">
-        <v/>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S5" t="n">
-        <v/>
-      </c>
-      <c r="T5" t="n">
-        <v/>
-      </c>
-      <c r="U5" t="n">
-        <v/>
-      </c>
-      <c r="V5" t="n">
-        <v/>
-      </c>
-      <c r="W5" t="n">
-        <v/>
-      </c>
-      <c r="X5" t="n">
-        <v/>
-      </c>
-      <c r="Y5" t="n">
-        <v/>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S6" t="n">
-        <v/>
-      </c>
-      <c r="T6" t="n">
-        <v/>
-      </c>
-      <c r="U6" t="n">
-        <v/>
-      </c>
-      <c r="V6" t="n">
-        <v/>
-      </c>
-      <c r="W6" t="n">
-        <v/>
-      </c>
-      <c r="X6" t="n">
-        <v/>
-      </c>
-      <c r="Y6" t="n">
-        <v/>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>187</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>171</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v/>
-      </c>
-      <c r="T10" t="n">
-        <v/>
-      </c>
-      <c r="U10" t="n">
-        <v/>
-      </c>
-      <c r="V10" t="n">
-        <v/>
-      </c>
-      <c r="W10" t="n">
-        <v/>
-      </c>
-      <c r="X10" t="n">
-        <v/>
-      </c>
-      <c r="Y10" t="n">
-        <v/>
-      </c>
-      <c r="Z10" t="n">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -703,14 +703,23 @@
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
     <col width="5" customWidth="1" min="30" max="30"/>
     <col width="5" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
     <col width="5" customWidth="1" min="33" max="33"/>
     <col width="5" customWidth="1" min="34" max="34"/>
     <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="2" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="9" customWidth="1" min="38" max="38"/>
+    <col width="5" customWidth="1" min="39" max="39"/>
+    <col width="5" customWidth="1" min="40" max="40"/>
+    <col width="5" customWidth="1" min="41" max="41"/>
+    <col width="5" customWidth="1" min="42" max="42"/>
+    <col width="5" customWidth="1" min="43" max="43"/>
+    <col width="5" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -874,164 +883,244 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1040,124 +1129,124 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="AB3" t="n">
         <v/>
       </c>
@@ -1180,130 +1269,154 @@
         <v/>
       </c>
       <c r="AI3" t="n">
+        <v/>
+      </c>
+      <c r="AK3" t="n">
+        <v/>
+      </c>
+      <c r="AL3" t="n">
+        <v/>
+      </c>
+      <c r="AM3" t="n">
+        <v/>
+      </c>
+      <c r="AN3" t="n">
+        <v/>
+      </c>
+      <c r="AO3" t="n">
+        <v/>
+      </c>
+      <c r="AP3" t="n">
+        <v/>
+      </c>
+      <c r="AQ3" t="n">
+        <v/>
+      </c>
+      <c r="AR3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="AB4" t="n">
         <v/>
       </c>
@@ -1326,130 +1439,154 @@
         <v/>
       </c>
       <c r="AI4" t="n">
+        <v/>
+      </c>
+      <c r="AK4" t="n">
+        <v/>
+      </c>
+      <c r="AL4" t="n">
+        <v/>
+      </c>
+      <c r="AM4" t="n">
+        <v/>
+      </c>
+      <c r="AN4" t="n">
+        <v/>
+      </c>
+      <c r="AO4" t="n">
+        <v/>
+      </c>
+      <c r="AP4" t="n">
+        <v/>
+      </c>
+      <c r="AQ4" t="n">
+        <v/>
+      </c>
+      <c r="AR4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="AB5" t="n">
         <v/>
       </c>
@@ -1472,130 +1609,154 @@
         <v/>
       </c>
       <c r="AI5" t="n">
+        <v/>
+      </c>
+      <c r="AK5" t="n">
+        <v/>
+      </c>
+      <c r="AL5" t="n">
+        <v/>
+      </c>
+      <c r="AM5" t="n">
+        <v/>
+      </c>
+      <c r="AN5" t="n">
+        <v/>
+      </c>
+      <c r="AO5" t="n">
+        <v/>
+      </c>
+      <c r="AP5" t="n">
+        <v/>
+      </c>
+      <c r="AQ5" t="n">
+        <v/>
+      </c>
+      <c r="AR5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="AB6" t="n">
         <v/>
       </c>
@@ -1618,130 +1779,154 @@
         <v/>
       </c>
       <c r="AI6" t="n">
+        <v/>
+      </c>
+      <c r="AK6" t="n">
+        <v/>
+      </c>
+      <c r="AL6" t="n">
+        <v/>
+      </c>
+      <c r="AM6" t="n">
+        <v/>
+      </c>
+      <c r="AN6" t="n">
+        <v/>
+      </c>
+      <c r="AO6" t="n">
+        <v/>
+      </c>
+      <c r="AP6" t="n">
+        <v/>
+      </c>
+      <c r="AQ6" t="n">
+        <v/>
+      </c>
+      <c r="AR6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="AB7" t="n">
         <v/>
       </c>
@@ -1764,130 +1949,154 @@
         <v/>
       </c>
       <c r="AI7" t="n">
+        <v/>
+      </c>
+      <c r="AK7" t="n">
+        <v/>
+      </c>
+      <c r="AL7" t="n">
+        <v/>
+      </c>
+      <c r="AM7" t="n">
+        <v/>
+      </c>
+      <c r="AN7" t="n">
+        <v/>
+      </c>
+      <c r="AO7" t="n">
+        <v/>
+      </c>
+      <c r="AP7" t="n">
+        <v/>
+      </c>
+      <c r="AQ7" t="n">
+        <v/>
+      </c>
+      <c r="AR7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="AB8" t="n">
         <v/>
       </c>
@@ -1910,130 +2119,154 @@
         <v/>
       </c>
       <c r="AI8" t="n">
+        <v/>
+      </c>
+      <c r="AK8" t="n">
+        <v/>
+      </c>
+      <c r="AL8" t="n">
+        <v/>
+      </c>
+      <c r="AM8" t="n">
+        <v/>
+      </c>
+      <c r="AN8" t="n">
+        <v/>
+      </c>
+      <c r="AO8" t="n">
+        <v/>
+      </c>
+      <c r="AP8" t="n">
+        <v/>
+      </c>
+      <c r="AQ8" t="n">
+        <v/>
+      </c>
+      <c r="AR8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="AB9" t="n">
         <v/>
       </c>
@@ -2056,120 +2289,144 @@
         <v/>
       </c>
       <c r="AI9" t="n">
+        <v/>
+      </c>
+      <c r="AK9" t="n">
+        <v/>
+      </c>
+      <c r="AL9" t="n">
+        <v/>
+      </c>
+      <c r="AM9" t="n">
+        <v/>
+      </c>
+      <c r="AN9" t="n">
+        <v/>
+      </c>
+      <c r="AO9" t="n">
+        <v/>
+      </c>
+      <c r="AP9" t="n">
+        <v/>
+      </c>
+      <c r="AQ9" t="n">
+        <v/>
+      </c>
+      <c r="AR9" t="n">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>189</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>187</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>0</t>
@@ -2202,6 +2459,30 @@
         <v/>
       </c>
       <c r="AI10" t="n">
+        <v/>
+      </c>
+      <c r="AK10" t="n">
+        <v/>
+      </c>
+      <c r="AL10" t="n">
+        <v/>
+      </c>
+      <c r="AM10" t="n">
+        <v/>
+      </c>
+      <c r="AN10" t="n">
+        <v/>
+      </c>
+      <c r="AO10" t="n">
+        <v/>
+      </c>
+      <c r="AP10" t="n">
+        <v/>
+      </c>
+      <c r="AQ10" t="n">
+        <v/>
+      </c>
+      <c r="AR10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR10"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -703,23 +703,14 @@
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
     <col width="5" customWidth="1" min="30" max="30"/>
     <col width="5" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
     <col width="5" customWidth="1" min="33" max="33"/>
     <col width="5" customWidth="1" min="34" max="34"/>
     <col width="5" customWidth="1" min="35" max="35"/>
-    <col width="2" customWidth="1" min="36" max="36"/>
-    <col width="15" customWidth="1" min="37" max="37"/>
-    <col width="9" customWidth="1" min="38" max="38"/>
-    <col width="5" customWidth="1" min="39" max="39"/>
-    <col width="5" customWidth="1" min="40" max="40"/>
-    <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="5" customWidth="1" min="42" max="42"/>
-    <col width="5" customWidth="1" min="43" max="43"/>
-    <col width="5" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -883,196 +874,156 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>24-April-2026</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>dsl</t>
+          <t>adminui</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1081,46 +1032,6 @@
         </is>
       </c>
       <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1129,124 +1040,124 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="AB3" t="n">
         <v/>
       </c>
@@ -1269,154 +1180,130 @@
         <v/>
       </c>
       <c r="AI3" t="n">
-        <v/>
-      </c>
-      <c r="AK3" t="n">
-        <v/>
-      </c>
-      <c r="AL3" t="n">
-        <v/>
-      </c>
-      <c r="AM3" t="n">
-        <v/>
-      </c>
-      <c r="AN3" t="n">
-        <v/>
-      </c>
-      <c r="AO3" t="n">
-        <v/>
-      </c>
-      <c r="AP3" t="n">
-        <v/>
-      </c>
-      <c r="AQ3" t="n">
-        <v/>
-      </c>
-      <c r="AR3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="AB4" t="n">
         <v/>
       </c>
@@ -1439,154 +1326,130 @@
         <v/>
       </c>
       <c r="AI4" t="n">
-        <v/>
-      </c>
-      <c r="AK4" t="n">
-        <v/>
-      </c>
-      <c r="AL4" t="n">
-        <v/>
-      </c>
-      <c r="AM4" t="n">
-        <v/>
-      </c>
-      <c r="AN4" t="n">
-        <v/>
-      </c>
-      <c r="AO4" t="n">
-        <v/>
-      </c>
-      <c r="AP4" t="n">
-        <v/>
-      </c>
-      <c r="AQ4" t="n">
-        <v/>
-      </c>
-      <c r="AR4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="AB5" t="n">
         <v/>
       </c>
@@ -1609,154 +1472,130 @@
         <v/>
       </c>
       <c r="AI5" t="n">
-        <v/>
-      </c>
-      <c r="AK5" t="n">
-        <v/>
-      </c>
-      <c r="AL5" t="n">
-        <v/>
-      </c>
-      <c r="AM5" t="n">
-        <v/>
-      </c>
-      <c r="AN5" t="n">
-        <v/>
-      </c>
-      <c r="AO5" t="n">
-        <v/>
-      </c>
-      <c r="AP5" t="n">
-        <v/>
-      </c>
-      <c r="AQ5" t="n">
-        <v/>
-      </c>
-      <c r="AR5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="AB6" t="n">
         <v/>
       </c>
@@ -1779,154 +1618,130 @@
         <v/>
       </c>
       <c r="AI6" t="n">
-        <v/>
-      </c>
-      <c r="AK6" t="n">
-        <v/>
-      </c>
-      <c r="AL6" t="n">
-        <v/>
-      </c>
-      <c r="AM6" t="n">
-        <v/>
-      </c>
-      <c r="AN6" t="n">
-        <v/>
-      </c>
-      <c r="AO6" t="n">
-        <v/>
-      </c>
-      <c r="AP6" t="n">
-        <v/>
-      </c>
-      <c r="AQ6" t="n">
-        <v/>
-      </c>
-      <c r="AR6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="AB7" t="n">
         <v/>
       </c>
@@ -1949,154 +1764,130 @@
         <v/>
       </c>
       <c r="AI7" t="n">
-        <v/>
-      </c>
-      <c r="AK7" t="n">
-        <v/>
-      </c>
-      <c r="AL7" t="n">
-        <v/>
-      </c>
-      <c r="AM7" t="n">
-        <v/>
-      </c>
-      <c r="AN7" t="n">
-        <v/>
-      </c>
-      <c r="AO7" t="n">
-        <v/>
-      </c>
-      <c r="AP7" t="n">
-        <v/>
-      </c>
-      <c r="AQ7" t="n">
-        <v/>
-      </c>
-      <c r="AR7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="AB8" t="n">
         <v/>
       </c>
@@ -2119,154 +1910,130 @@
         <v/>
       </c>
       <c r="AI8" t="n">
-        <v/>
-      </c>
-      <c r="AK8" t="n">
-        <v/>
-      </c>
-      <c r="AL8" t="n">
-        <v/>
-      </c>
-      <c r="AM8" t="n">
-        <v/>
-      </c>
-      <c r="AN8" t="n">
-        <v/>
-      </c>
-      <c r="AO8" t="n">
-        <v/>
-      </c>
-      <c r="AP8" t="n">
-        <v/>
-      </c>
-      <c r="AQ8" t="n">
-        <v/>
-      </c>
-      <c r="AR8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="AB9" t="n">
         <v/>
       </c>
@@ -2289,144 +2056,120 @@
         <v/>
       </c>
       <c r="AI9" t="n">
-        <v/>
-      </c>
-      <c r="AK9" t="n">
-        <v/>
-      </c>
-      <c r="AL9" t="n">
-        <v/>
-      </c>
-      <c r="AM9" t="n">
-        <v/>
-      </c>
-      <c r="AN9" t="n">
-        <v/>
-      </c>
-      <c r="AO9" t="n">
-        <v/>
-      </c>
-      <c r="AP9" t="n">
-        <v/>
-      </c>
-      <c r="AQ9" t="n">
-        <v/>
-      </c>
-      <c r="AR9" t="n">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>189</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>0</t>
@@ -2459,30 +2202,6 @@
         <v/>
       </c>
       <c r="AI10" t="n">
-        <v/>
-      </c>
-      <c r="AK10" t="n">
-        <v/>
-      </c>
-      <c r="AL10" t="n">
-        <v/>
-      </c>
-      <c r="AM10" t="n">
-        <v/>
-      </c>
-      <c r="AN10" t="n">
-        <v/>
-      </c>
-      <c r="AO10" t="n">
-        <v/>
-      </c>
-      <c r="AP10" t="n">
-        <v/>
-      </c>
-      <c r="AQ10" t="n">
-        <v/>
-      </c>
-      <c r="AR10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -685,32 +685,14 @@
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -794,91 +776,11 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -918,22 +820,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>07-May-2026</t>
+          <t>24-April-2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>adminui</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -948,90 +850,10 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1040,7 +862,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1078,115 +900,35 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v/>
-      </c>
-      <c r="AC3" t="n">
-        <v/>
-      </c>
-      <c r="AD3" t="n">
-        <v/>
-      </c>
-      <c r="AE3" t="n">
-        <v/>
-      </c>
-      <c r="AF3" t="n">
-        <v/>
-      </c>
-      <c r="AG3" t="n">
-        <v/>
-      </c>
-      <c r="AH3" t="n">
-        <v/>
-      </c>
-      <c r="AI3" t="n">
+      <c r="J3" t="n">
+        <v/>
+      </c>
+      <c r="K3" t="n">
+        <v/>
+      </c>
+      <c r="L3" t="n">
+        <v/>
+      </c>
+      <c r="M3" t="n">
+        <v/>
+      </c>
+      <c r="N3" t="n">
+        <v/>
+      </c>
+      <c r="O3" t="n">
+        <v/>
+      </c>
+      <c r="P3" t="n">
+        <v/>
+      </c>
+      <c r="Q3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1224,115 +966,35 @@
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v/>
-      </c>
-      <c r="AC4" t="n">
-        <v/>
-      </c>
-      <c r="AD4" t="n">
-        <v/>
-      </c>
-      <c r="AE4" t="n">
-        <v/>
-      </c>
-      <c r="AF4" t="n">
-        <v/>
-      </c>
-      <c r="AG4" t="n">
-        <v/>
-      </c>
-      <c r="AH4" t="n">
-        <v/>
-      </c>
-      <c r="AI4" t="n">
+      <c r="J4" t="n">
+        <v/>
+      </c>
+      <c r="K4" t="n">
+        <v/>
+      </c>
+      <c r="L4" t="n">
+        <v/>
+      </c>
+      <c r="M4" t="n">
+        <v/>
+      </c>
+      <c r="N4" t="n">
+        <v/>
+      </c>
+      <c r="O4" t="n">
+        <v/>
+      </c>
+      <c r="P4" t="n">
+        <v/>
+      </c>
+      <c r="Q4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1370,115 +1032,35 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v/>
-      </c>
-      <c r="AC5" t="n">
-        <v/>
-      </c>
-      <c r="AD5" t="n">
-        <v/>
-      </c>
-      <c r="AE5" t="n">
-        <v/>
-      </c>
-      <c r="AF5" t="n">
-        <v/>
-      </c>
-      <c r="AG5" t="n">
-        <v/>
-      </c>
-      <c r="AH5" t="n">
-        <v/>
-      </c>
-      <c r="AI5" t="n">
+      <c r="J5" t="n">
+        <v/>
+      </c>
+      <c r="K5" t="n">
+        <v/>
+      </c>
+      <c r="L5" t="n">
+        <v/>
+      </c>
+      <c r="M5" t="n">
+        <v/>
+      </c>
+      <c r="N5" t="n">
+        <v/>
+      </c>
+      <c r="O5" t="n">
+        <v/>
+      </c>
+      <c r="P5" t="n">
+        <v/>
+      </c>
+      <c r="Q5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1516,115 +1098,35 @@
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1662,115 +1164,35 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1808,115 +1230,35 @@
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1954,115 +1296,35 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v/>
-      </c>
-      <c r="AC9" t="n">
-        <v/>
-      </c>
-      <c r="AD9" t="n">
-        <v/>
-      </c>
-      <c r="AE9" t="n">
-        <v/>
-      </c>
-      <c r="AF9" t="n">
-        <v/>
-      </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="n">
-        <v/>
-      </c>
-      <c r="AI9" t="n">
+      <c r="J9" t="n">
+        <v/>
+      </c>
+      <c r="K9" t="n">
+        <v/>
+      </c>
+      <c r="L9" t="n">
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v/>
+      </c>
+      <c r="N9" t="n">
+        <v/>
+      </c>
+      <c r="O9" t="n">
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v/>
+      </c>
+      <c r="Q9" t="n">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08-May-2026</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2077,7 +1339,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>191</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2087,7 +1349,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2100,108 +1362,28 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>07-May-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v/>
-      </c>
-      <c r="AC10" t="n">
-        <v/>
-      </c>
-      <c r="AD10" t="n">
-        <v/>
-      </c>
-      <c r="AE10" t="n">
-        <v/>
-      </c>
-      <c r="AF10" t="n">
-        <v/>
-      </c>
-      <c r="AG10" t="n">
-        <v/>
-      </c>
-      <c r="AH10" t="n">
-        <v/>
-      </c>
-      <c r="AI10" t="n">
+      <c r="J10" t="n">
+        <v/>
+      </c>
+      <c r="K10" t="n">
+        <v/>
+      </c>
+      <c r="L10" t="n">
+        <v/>
+      </c>
+      <c r="M10" t="n">
+        <v/>
+      </c>
+      <c r="N10" t="n">
+        <v/>
+      </c>
+      <c r="O10" t="n">
+        <v/>
+      </c>
+      <c r="P10" t="n">
+        <v/>
+      </c>
+      <c r="Q10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -685,14 +685,23 @@
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -776,84 +785,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -862,528 +951,848 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
+        <v/>
+      </c>
+      <c r="T3" t="n">
+        <v/>
+      </c>
+      <c r="U3" t="n">
+        <v/>
+      </c>
+      <c r="V3" t="n">
+        <v/>
+      </c>
+      <c r="W3" t="n">
+        <v/>
+      </c>
+      <c r="X3" t="n">
+        <v/>
+      </c>
+      <c r="Y3" t="n">
+        <v/>
+      </c>
+      <c r="Z3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
+        <v/>
+      </c>
+      <c r="T4" t="n">
+        <v/>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
+      </c>
+      <c r="Z4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
+        <v/>
+      </c>
+      <c r="T5" t="n">
+        <v/>
+      </c>
+      <c r="U5" t="n">
+        <v/>
+      </c>
+      <c r="V5" t="n">
+        <v/>
+      </c>
+      <c r="W5" t="n">
+        <v/>
+      </c>
+      <c r="X5" t="n">
+        <v/>
+      </c>
+      <c r="Y5" t="n">
+        <v/>
+      </c>
+      <c r="Z5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
+        <v/>
+      </c>
+      <c r="T6" t="n">
+        <v/>
+      </c>
+      <c r="U6" t="n">
+        <v/>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
+      </c>
+      <c r="Z6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v/>
+      </c>
+      <c r="T10" t="n">
+        <v/>
+      </c>
+      <c r="U10" t="n">
+        <v/>
+      </c>
+      <c r="V10" t="n">
+        <v/>
+      </c>
+      <c r="W10" t="n">
+        <v/>
+      </c>
+      <c r="X10" t="n">
+        <v/>
+      </c>
+      <c r="Y10" t="n">
+        <v/>
+      </c>
+      <c r="Z10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -694,14 +694,23 @@
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -825,124 +834,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -951,848 +1040,1168 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v/>
-      </c>
-      <c r="T3" t="n">
-        <v/>
-      </c>
-      <c r="U3" t="n">
-        <v/>
-      </c>
-      <c r="V3" t="n">
-        <v/>
-      </c>
-      <c r="W3" t="n">
-        <v/>
-      </c>
-      <c r="X3" t="n">
-        <v/>
-      </c>
-      <c r="Y3" t="n">
-        <v/>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S4" t="n">
-        <v/>
-      </c>
-      <c r="T4" t="n">
-        <v/>
-      </c>
-      <c r="U4" t="n">
-        <v/>
-      </c>
-      <c r="V4" t="n">
-        <v/>
-      </c>
-      <c r="W4" t="n">
-        <v/>
-      </c>
-      <c r="X4" t="n">
-        <v/>
-      </c>
-      <c r="Y4" t="n">
-        <v/>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S5" t="n">
-        <v/>
-      </c>
-      <c r="T5" t="n">
-        <v/>
-      </c>
-      <c r="U5" t="n">
-        <v/>
-      </c>
-      <c r="V5" t="n">
-        <v/>
-      </c>
-      <c r="W5" t="n">
-        <v/>
-      </c>
-      <c r="X5" t="n">
-        <v/>
-      </c>
-      <c r="Y5" t="n">
-        <v/>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S6" t="n">
-        <v/>
-      </c>
-      <c r="T6" t="n">
-        <v/>
-      </c>
-      <c r="U6" t="n">
-        <v/>
-      </c>
-      <c r="V6" t="n">
-        <v/>
-      </c>
-      <c r="W6" t="n">
-        <v/>
-      </c>
-      <c r="X6" t="n">
-        <v/>
-      </c>
-      <c r="Y6" t="n">
-        <v/>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1129</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v/>
-      </c>
-      <c r="T10" t="n">
-        <v/>
-      </c>
-      <c r="U10" t="n">
-        <v/>
-      </c>
-      <c r="V10" t="n">
-        <v/>
-      </c>
-      <c r="W10" t="n">
-        <v/>
-      </c>
-      <c r="X10" t="n">
-        <v/>
-      </c>
-      <c r="Y10" t="n">
-        <v/>
-      </c>
-      <c r="Z10" t="n">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -878,112 +878,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1040,87 +1040,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1186,87 +1186,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1332,87 +1332,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1478,87 +1478,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1624,87 +1624,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1770,87 +1770,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1916,87 +1916,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1129</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2062,112 +2062,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -878,104 +878,104 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>0</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1040,87 +1040,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1186,87 +1186,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1332,87 +1332,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1478,87 +1478,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1624,87 +1624,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1770,87 +1770,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1916,112 +1916,112 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1114</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1129</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2062,112 +2062,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -685,32 +685,14 @@
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -794,91 +776,11 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -918,22 +820,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14-May-2026</t>
+          <t>24-April-2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>auth</t>
+          <t>adminui</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -948,90 +850,10 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1040,7 +862,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1078,115 +900,35 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v/>
-      </c>
-      <c r="AC3" t="n">
-        <v/>
-      </c>
-      <c r="AD3" t="n">
-        <v/>
-      </c>
-      <c r="AE3" t="n">
-        <v/>
-      </c>
-      <c r="AF3" t="n">
-        <v/>
-      </c>
-      <c r="AG3" t="n">
-        <v/>
-      </c>
-      <c r="AH3" t="n">
-        <v/>
-      </c>
-      <c r="AI3" t="n">
+      <c r="J3" t="n">
+        <v/>
+      </c>
+      <c r="K3" t="n">
+        <v/>
+      </c>
+      <c r="L3" t="n">
+        <v/>
+      </c>
+      <c r="M3" t="n">
+        <v/>
+      </c>
+      <c r="N3" t="n">
+        <v/>
+      </c>
+      <c r="O3" t="n">
+        <v/>
+      </c>
+      <c r="P3" t="n">
+        <v/>
+      </c>
+      <c r="Q3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1224,115 +966,35 @@
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v/>
-      </c>
-      <c r="AC4" t="n">
-        <v/>
-      </c>
-      <c r="AD4" t="n">
-        <v/>
-      </c>
-      <c r="AE4" t="n">
-        <v/>
-      </c>
-      <c r="AF4" t="n">
-        <v/>
-      </c>
-      <c r="AG4" t="n">
-        <v/>
-      </c>
-      <c r="AH4" t="n">
-        <v/>
-      </c>
-      <c r="AI4" t="n">
+      <c r="J4" t="n">
+        <v/>
+      </c>
+      <c r="K4" t="n">
+        <v/>
+      </c>
+      <c r="L4" t="n">
+        <v/>
+      </c>
+      <c r="M4" t="n">
+        <v/>
+      </c>
+      <c r="N4" t="n">
+        <v/>
+      </c>
+      <c r="O4" t="n">
+        <v/>
+      </c>
+      <c r="P4" t="n">
+        <v/>
+      </c>
+      <c r="Q4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1370,115 +1032,35 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v/>
-      </c>
-      <c r="AC5" t="n">
-        <v/>
-      </c>
-      <c r="AD5" t="n">
-        <v/>
-      </c>
-      <c r="AE5" t="n">
-        <v/>
-      </c>
-      <c r="AF5" t="n">
-        <v/>
-      </c>
-      <c r="AG5" t="n">
-        <v/>
-      </c>
-      <c r="AH5" t="n">
-        <v/>
-      </c>
-      <c r="AI5" t="n">
+      <c r="J5" t="n">
+        <v/>
+      </c>
+      <c r="K5" t="n">
+        <v/>
+      </c>
+      <c r="L5" t="n">
+        <v/>
+      </c>
+      <c r="M5" t="n">
+        <v/>
+      </c>
+      <c r="N5" t="n">
+        <v/>
+      </c>
+      <c r="O5" t="n">
+        <v/>
+      </c>
+      <c r="P5" t="n">
+        <v/>
+      </c>
+      <c r="Q5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1516,115 +1098,35 @@
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1662,115 +1164,35 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1808,115 +1230,35 @@
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1931,7 +1273,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1941,7 +1283,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1954,115 +1296,35 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1114</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1129</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v/>
-      </c>
-      <c r="AC9" t="n">
-        <v/>
-      </c>
-      <c r="AD9" t="n">
-        <v/>
-      </c>
-      <c r="AE9" t="n">
-        <v/>
-      </c>
-      <c r="AF9" t="n">
-        <v/>
-      </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="n">
-        <v/>
-      </c>
-      <c r="AI9" t="n">
+      <c r="J9" t="n">
+        <v/>
+      </c>
+      <c r="K9" t="n">
+        <v/>
+      </c>
+      <c r="L9" t="n">
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v/>
+      </c>
+      <c r="N9" t="n">
+        <v/>
+      </c>
+      <c r="O9" t="n">
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v/>
+      </c>
+      <c r="Q9" t="n">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>18-May-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2100,108 +1362,28 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v/>
-      </c>
-      <c r="AC10" t="n">
-        <v/>
-      </c>
-      <c r="AD10" t="n">
-        <v/>
-      </c>
-      <c r="AE10" t="n">
-        <v/>
-      </c>
-      <c r="AF10" t="n">
-        <v/>
-      </c>
-      <c r="AG10" t="n">
-        <v/>
-      </c>
-      <c r="AH10" t="n">
-        <v/>
-      </c>
-      <c r="AI10" t="n">
+      <c r="J10" t="n">
+        <v/>
+      </c>
+      <c r="K10" t="n">
+        <v/>
+      </c>
+      <c r="L10" t="n">
+        <v/>
+      </c>
+      <c r="M10" t="n">
+        <v/>
+      </c>
+      <c r="N10" t="n">
+        <v/>
+      </c>
+      <c r="O10" t="n">
+        <v/>
+      </c>
+      <c r="P10" t="n">
+        <v/>
+      </c>
+      <c r="Q10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -685,14 +685,23 @@
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -776,84 +785,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -862,528 +951,848 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
+        <v/>
+      </c>
+      <c r="T3" t="n">
+        <v/>
+      </c>
+      <c r="U3" t="n">
+        <v/>
+      </c>
+      <c r="V3" t="n">
+        <v/>
+      </c>
+      <c r="W3" t="n">
+        <v/>
+      </c>
+      <c r="X3" t="n">
+        <v/>
+      </c>
+      <c r="Y3" t="n">
+        <v/>
+      </c>
+      <c r="Z3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
+        <v/>
+      </c>
+      <c r="T4" t="n">
+        <v/>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
+      </c>
+      <c r="Z4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
+        <v/>
+      </c>
+      <c r="T5" t="n">
+        <v/>
+      </c>
+      <c r="U5" t="n">
+        <v/>
+      </c>
+      <c r="V5" t="n">
+        <v/>
+      </c>
+      <c r="W5" t="n">
+        <v/>
+      </c>
+      <c r="X5" t="n">
+        <v/>
+      </c>
+      <c r="Y5" t="n">
+        <v/>
+      </c>
+      <c r="Z5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
+        <v/>
+      </c>
+      <c r="T6" t="n">
+        <v/>
+      </c>
+      <c r="U6" t="n">
+        <v/>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
+      </c>
+      <c r="Z6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1129</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v/>
+      </c>
+      <c r="T10" t="n">
+        <v/>
+      </c>
+      <c r="U10" t="n">
+        <v/>
+      </c>
+      <c r="V10" t="n">
+        <v/>
+      </c>
+      <c r="W10" t="n">
+        <v/>
+      </c>
+      <c r="X10" t="n">
+        <v/>
+      </c>
+      <c r="Y10" t="n">
+        <v/>
+      </c>
+      <c r="Z10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -694,14 +694,23 @@
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -825,124 +834,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -951,848 +1040,1168 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v/>
-      </c>
-      <c r="T3" t="n">
-        <v/>
-      </c>
-      <c r="U3" t="n">
-        <v/>
-      </c>
-      <c r="V3" t="n">
-        <v/>
-      </c>
-      <c r="W3" t="n">
-        <v/>
-      </c>
-      <c r="X3" t="n">
-        <v/>
-      </c>
-      <c r="Y3" t="n">
-        <v/>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S4" t="n">
-        <v/>
-      </c>
-      <c r="T4" t="n">
-        <v/>
-      </c>
-      <c r="U4" t="n">
-        <v/>
-      </c>
-      <c r="V4" t="n">
-        <v/>
-      </c>
-      <c r="W4" t="n">
-        <v/>
-      </c>
-      <c r="X4" t="n">
-        <v/>
-      </c>
-      <c r="Y4" t="n">
-        <v/>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S5" t="n">
-        <v/>
-      </c>
-      <c r="T5" t="n">
-        <v/>
-      </c>
-      <c r="U5" t="n">
-        <v/>
-      </c>
-      <c r="V5" t="n">
-        <v/>
-      </c>
-      <c r="W5" t="n">
-        <v/>
-      </c>
-      <c r="X5" t="n">
-        <v/>
-      </c>
-      <c r="Y5" t="n">
-        <v/>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S6" t="n">
-        <v/>
-      </c>
-      <c r="T6" t="n">
-        <v/>
-      </c>
-      <c r="U6" t="n">
-        <v/>
-      </c>
-      <c r="V6" t="n">
-        <v/>
-      </c>
-      <c r="W6" t="n">
-        <v/>
-      </c>
-      <c r="X6" t="n">
-        <v/>
-      </c>
-      <c r="Y6" t="n">
-        <v/>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1129</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v/>
-      </c>
-      <c r="T10" t="n">
-        <v/>
-      </c>
-      <c r="U10" t="n">
-        <v/>
-      </c>
-      <c r="V10" t="n">
-        <v/>
-      </c>
-      <c r="W10" t="n">
-        <v/>
-      </c>
-      <c r="X10" t="n">
-        <v/>
-      </c>
-      <c r="Y10" t="n">
-        <v/>
-      </c>
-      <c r="Z10" t="n">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -878,87 +878,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1040,87 +1040,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1186,112 +1186,112 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1332,87 +1332,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1478,87 +1478,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>906</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1624,87 +1624,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1770,87 +1770,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1916,104 +1916,104 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1129</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2062,87 +2062,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa11.xlsx
+++ b/minio-report-tracker/xlxs/qa11.xlsx
@@ -878,87 +878,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1040,87 +1040,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1186,104 +1186,104 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1332,87 +1332,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1478,112 +1478,112 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>906</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1624,87 +1624,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1770,87 +1770,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1916,87 +1916,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1129</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2062,87 +2062,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
